--- a/docentes/Valerio González Valeria - Estadisticos 20231.xlsx
+++ b/docentes/Valerio González Valeria - Estadisticos 20231.xlsx
@@ -513,10 +513,10 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>10</v>
@@ -525,7 +525,7 @@
         <v>2</v>
       </c>
       <c r="G2">
-        <v>14.29</v>
+        <v>16.67</v>
       </c>
       <c r="H2">
         <v>4.8</v>
@@ -578,10 +578,10 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E2">
         <v>12</v>
@@ -640,10 +640,10 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>10</v>
@@ -652,7 +652,7 @@
         <v>2</v>
       </c>
       <c r="G2">
-        <v>14.29</v>
+        <v>16.67</v>
       </c>
       <c r="H2">
         <v>5.3</v>

--- a/docentes/Valerio González Valeria - Estadisticos 20231.xlsx
+++ b/docentes/Valerio González Valeria - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -67,55 +67,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>MIXCOHA</t>
-  </si>
-  <si>
-    <t>GALICIA</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>CRISTHIAN ALFONSO</t>
-  </si>
-  <si>
-    <t>ROGELIO</t>
-  </si>
-  <si>
-    <t>JOSE RUBEN</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>PEDRO ANGEL</t>
+  </si>
+  <si>
+    <t>LUIS GUILLERMO</t>
   </si>
 </sst>
 </file>
@@ -581,16 +548,19 @@
         <v>12</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>83.33</v>
+      </c>
+      <c r="H2">
+        <v>4.8</v>
       </c>
     </row>
   </sheetData>
@@ -646,16 +616,16 @@
         <v>0</v>
       </c>
       <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
         <v>10</v>
       </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
       <c r="G2">
-        <v>16.67</v>
+        <v>83.33</v>
       </c>
       <c r="H2">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
     </row>
   </sheetData>
@@ -665,7 +635,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -697,16 +667,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920139</v>
+        <v>21330051920135</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -720,16 +690,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920148</v>
+        <v>21330051920382</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -739,98 +709,6 @@
       </c>
       <c r="G3">
         <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920138</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920146</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920150</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920392</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Valerio González Valeria - Estadisticos 20231.xlsx
+++ b/docentes/Valerio González Valeria - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="16">
   <si>
     <t>Mat</t>
   </si>
@@ -65,24 +65,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>PEDRO ANGEL</t>
-  </si>
-  <si>
-    <t>LUIS GUILLERMO</t>
   </si>
 </sst>
 </file>
@@ -635,7 +617,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -665,52 +647,6 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920135</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920382</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Valerio González Valeria - Estadisticos 20231.xlsx
+++ b/docentes/Valerio González Valeria - Estadisticos 20231.xlsx
@@ -462,7 +462,7 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -471,13 +471,13 @@
         <v>10</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>16.67</v>
+        <v>23.08</v>
       </c>
       <c r="H2">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
     </row>
   </sheetData>
@@ -527,7 +527,7 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -536,13 +536,13 @@
         <v>2</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="H2">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
     </row>
   </sheetData>
@@ -592,7 +592,7 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -601,13 +601,13 @@
         <v>2</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Valerio González Valeria - Estadisticos 20231.xlsx
+++ b/docentes/Valerio González Valeria - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="19">
   <si>
     <t>Mat</t>
   </si>
@@ -65,6 +65,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>PEDRO ANGEL</t>
   </si>
 </sst>
 </file>
@@ -607,7 +616,7 @@
         <v>84.62</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -617,7 +626,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -647,6 +656,29 @@
         <v>15</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>21330051920135</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Valerio González Valeria - Estadisticos 20231.xlsx
+++ b/docentes/Valerio González Valeria - Estadisticos 20231.xlsx
@@ -676,7 +676,7 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Valerio González Valeria - Estadisticos 20231.xlsx
+++ b/docentes/Valerio González Valeria - Estadisticos 20231.xlsx
@@ -616,7 +616,7 @@
         <v>84.62</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Valerio González Valeria - Estadisticos 20231.xlsx
+++ b/docentes/Valerio González Valeria - Estadisticos 20231.xlsx
@@ -616,7 +616,7 @@
         <v>84.62</v>
       </c>
       <c r="H2">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
